--- a/summary of beneficiaries.xlsx
+++ b/summary of beneficiaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\sdsg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B4A7B0C-95F5-458B-9B28-4EB73D3945FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64890ADD-41D2-49D9-8210-449102C16D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{78EBCA44-9757-4FFB-843F-1C7AF65D41A7}"/>
   </bookViews>
